--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2019_metropolitana.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2019_metropolitana.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:02</t>
+    <t xml:space="preserve">2026-09-24 00:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -944,7 +944,7 @@
         <v>-0.79</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>-0.02</v>
@@ -967,7 +967,7 @@
         <v>-0.27</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>-0.24</v>
@@ -990,7 +990,7 @@
         <v>-0.66</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0.13</v>
@@ -1004,19 +1004,19 @@
         <v>26</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>52</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.4</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="22">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2019_metropolitana.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2019_metropolitana.xlsx
@@ -117,7 +117,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:53</t>
+    <t xml:space="preserve">2026-10-01 23:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2019_metropolitana.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2019_metropolitana.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:17</t>
+    <t xml:space="preserve">2026-10-05 19:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
